--- a/human_validation/judge/kor/judge_D003_S001_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D003_S001_P001__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,82 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오셨는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 정리정돈을 유지하는 게 너무 힘들어서 왔어요. 그러니까, 학교 공부도 있고 작은 액세서리 매장도 운영하고 있는데, 재료, 마감일, 영수증, 과제 메모 같은 게 계속 쌓여요. 뭘 먼저 해야 할지 몰라서 그냥 막혀버리고, 이게 점점 감당이 안 될 정도가 되고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 일들을 다 관리하려고 할 때 특히, 자주 불안하거나 걱정된다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 일이 쌓일 때 스트레스를 받긴 하는데, 그걸 자주 불안하다고 불러야 할지는 모르겠어요. 그보다는 처리할 게 너무 많을 때 그 순간에 벅차다고 느끼는 쪽에 가까워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 특별히 스트레스를 유발하는 일이나 과제가 없을 때도 불안하거나 신경이 곤두선다고 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 그런 건 아닌 것 같아요. 보통 이유 없이 신경이 곤두서지는 않아요. 그보다는 눈앞에 뭔가 너무 많다고 느껴지거나 한꺼번에 여러 가지를 챙기려고 할 때 그런 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>진단명: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)
 인구통계: 성별 여성 / 나이 21 / 직업상태 not in workforce / 최종학력 고등학교 졸업
@@ -575,140 +642,39 @@
 증상 지속 기간: 2 years and 2 months
 추가 요건: Onset prior to age 12 years
 주호소 증상 코드: S005
-배경 서술: 캐슬린은 익숙했던 지역 생활 루틴에서 벗어나 경영학 과정에 등록하는 동시에 수제 액세서리 매장을 운영하려 하면서, 느슨한 일정과 겹치는 마감일들이 그동안 그녀를 지탱해 주던 외부적인 구조들을 많이 걷어내 버렸다. 이후 2년 2개월 동안, 그녀는 과제와 매장 주문에 대한 지시사항을 점점 놓치게 되었고, 프로젝트를 끝맺지 못한 채 남겨두었으며, 재고와 과제를 정리하는 데 어려움을 겪었고, 수업이나 스터디 그룹, 거래처 미팅에서 눈에 띄게 안절부절못하는 모습을 보였다. 대화에 불쑥 끼어들거나 다른 사람이 말을 끝내기 전에 대답하고, 그룹 피드백 시간에 차례를 기다리는 데 어려움을 겪는 습관은 성적과 협업, 그리고 그녀가 소중히 여기던 사업 계획을 끝까지 추진하는 능력에 영향을 미치기 시작했다. 일련의 학업 요건을 놓치면서 학자금 지원과 과정 이수 자격이 위태로워지자, 그녀는 대학 상담센터를 통해 도움을 구했고 정신과 평가를 의뢰받았다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오셨는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 정리정돈을 유지하는 게 너무 힘들어서 왔어요. 그러니까, 학교 공부도 있고 작은 액세서리 매장도 운영하고 있는데, 재료, 마감일, 영수증, 과제 메모 같은 게 계속 쌓여요. 뭘 먼저 해야 할지 몰라서 그냥 막혀버리고, 이게 점점 감당이 안 될 정도가 되고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 일들을 다 관리하려고 할 때 특히, 자주 불안하거나 걱정된다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 일이 쌓일 때 스트레스를 받긴 하는데, 그걸 자주 불안하다고 불러야 할지는 모르겠어요. 그보다는 처리할 게 너무 많을 때 그 순간에 벅차다고 느끼는 쪽에 가까워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 특별히 스트레스를 유발하는 일이나 과제가 없을 때도 불안하거나 신경이 곤두선다고 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 그런 건 아닌 것 같아요. 보통 이유 없이 신경이 곤두서지는 않아요. 그보다는 눈앞에 뭔가 너무 많다고 느껴지거나 한꺼번에 여러 가지를 챙기려고 할 때 그런 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+배경 서술: 캐슬린은 익숙했던 지역 생활 루틴에서 벗어나 경영학 과정에 등록하는 동시에 수제 액세서리 매장을 운영하려 하면서, 느슨한 일정과 겹치는 마감일들이 그동안 그녀를 지탱해 주던 외부적인 구조들을 많이 걷어내 버렸다. 이후 2년 2개월 동안, 그녀는 과제와 매장 주문에 대한 지시사항을 점점 놓치게 되었고, 프로젝트를 끝맺지 못한 채 남겨두었으며, 재고와 과제를 정리하는 데 어려움을 겪었고, 수업이나 스터디 그룹, 거래처 미팅에서 눈에 띄게 안절부절못하는 모습을 보였다. 대화에 불쑥 끼어들거나 다른 사람이 말을 끝내기 전에 대답하고, 그룹 피드백 시간에 차례를 기다리는 데 어려움을 겪는 습관은 성적과 협업, 그리고 그녀가 소중히 여기던 사업 계획을 끝까지 추진하는 능력에 영향을 미치기 시작했다. 일련의 학업 요건을 놓치면서 학자금 지원과 과정 이수 자격이 위태로워지자, 그녀는 대학 상담센터를 통해 도움을 구했고 정신과 평가를 의뢰받았다.
+표집된 증상 목록:
+  - S002 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.
+  - S004 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.
+  - S005 조직화 곤란: 과제와 활동을 체계적으로 조직하는 데 자주 어려움을 겪는다.
+  - S010 손발 꼼지락거림: 손발을 가만두지 못하고 두드리거나 자리에서 꼼지락거리는 경우가 잦다.
+  - S011 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.
+  - S012 안절부절못함: 부적절한 상황에서 자주 뛰어다니거나 기어오른다(청소년/성인의 경우 안절부절못하는 느낌으로 제한될 수 있다).
+  - S016 성급한 대답: 질문이 끝나기도 전에 불쑥 대답해버리는 경우가 잦다.
+  - S017 차례 기다리기 곤란: 차례를 기다리는 데 자주 어려움을 겪는다.</t>
+        </is>
+      </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주의력결핍 과잉행동장애 (부주의 우세형) (D002, ICD: F90.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: inattention (관계=include, 요구개수=5, 충족개수=1, 커버리지=0.2)
-  확인된 근거: 조직화 곤란: 과제와 활동을 체계적으로 조직하는 데 자주 어려움을 겪는다.
-  누락: 세부사항 부주의 실수: 세부적인 것에 주의를 기울이지 못하거나 부주의한 실수를 자주 한다.; 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.; 경청 곤란: 직접 말을 걸어도 듣지 않는 것처럼 보이는 경우가 잦다.; 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.; 지속적 정신적 노력 회피: 지속적인 정신적 노력을 요하는 과제를 자주 피하거나 싫어하거나 꺼린다.; 물건 분실: 과제나 활동에 필요한 물건을 자주 잃어버린다.; 산만함: 외부 자극에 의해 쉽게 주의가 분산된다(청소년 후기 및 성인의 경우 관련 없는 생각도 포함될 수 있다).; 일상 활동 망각: 일상 활동에서 자주 잊어버린다(예: 집안일, 심부름, 성인의 경우 전화 회신, 청구서 납부, 약속 지키기 등).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: hyperactivity_impulsivity (관계=must_include, 요구개수=5, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 손발 꼼지락거림: 손발을 가만두지 못하고 두드리거나 자리에서 꼼지락거리는 경우가 잦다.; 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.; 안절부절못함: 부적절한 상황에서 자주 뛰어다니거나 기어오른다(청소년/성인의 경우 안절부절못하는 느낌으로 제한될 수 있다).; 조용한 활동 곤란: 여가 활동을 조용히 하지 못하는 경우가 잦다.; 끊임없는 활동성: 마치 '모터가 달린 것처럼' 끊임없이 활동한다.; 과도한 말하기: 지나치게 말을 많이 하는 경우가 잦다.; 성급한 대답: 질문이 끝나기도 전에 불쑥 대답해버리는 경우가 잦다.; 차례 기다리기 곤란: 차례를 기다리는 데 자주 어려움을 겪는다.; 끼어들기/방해: 다른 사람의 대화나 활동에 자주 끼어들거나 방해한다(예: 대화, 게임, 활동에 불쑥 끼어듦).</t>
+          <t>의사의 최종 진단: 주의력결핍 과잉행동장애 (부주의 우세형) (D002, ICD: F90.0)
+지속 기간 요건: 없음
+기능적 손상 요건: 없음
+추가 요건: 없음
+체크리스트 그룹: inattention (관계=include, 요구개수=5, 충족개수=1, 커버리지=0.2)
+확인된 근거:
+  - 조직화 곤란: 과제와 활동을 체계적으로 조직하는 데 자주 어려움을 겪는다.
+체크리스트 그룹: hyperactivity_impulsivity (관계=must_include, 요구개수=5, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D003_S001_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D003_S001_P001__qwen3-235b_kor.xlsx
@@ -628,6 +628,11 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -670,11 +675,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D003_S001_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D003_S001_P001__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -555,6 +556,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
